--- a/data/db.xlsx
+++ b/data/db.xlsx
@@ -5,17 +5,21 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smaruf\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smaruf\Downloads\payroll\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48F84C4-6D69-423E-977C-02AC2769429C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1CF7650-95A7-4263-9998-3DE8B8AA1A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="3630" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{6F5C9924-9F49-4F1B-B94C-A9862A11C87B}"/>
+    <workbookView xWindow="5385" yWindow="3945" windowWidth="28800" windowHeight="15345" xr2:uid="{6F5C9924-9F49-4F1B-B94C-A9862A11C87B}"/>
   </bookViews>
   <sheets>
     <sheet name="casual" sheetId="1" r:id="rId1"/>
     <sheet name="fixedterm_Ongoing" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="payincrease5">fixedterm_Ongoing!$BE$11</definedName>
+    <definedName name="payincrease6">fixedterm_Ongoing!$BE$12</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -845,7 +849,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -857,16 +861,12 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -881,6 +881,13 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1216,16 +1223,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DA37E77-72C3-46FF-B3E3-26ADEE1FFFE9}">
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="78.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B1" s="2"/>
-      <c r="C1" s="7">
+      <c r="C1" s="6">
         <v>45839</v>
       </c>
     </row>
@@ -1236,7 +1243,7 @@
       <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="19" t="s">
         <v>217</v>
       </c>
     </row>
@@ -1247,8 +1254,8 @@
       <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5">
-        <v>375.46382864315819</v>
+      <c r="C3" s="23">
+        <v>375.46</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1258,8 +1265,8 @@
       <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="5">
-        <v>300.37572170819402</v>
+      <c r="C4" s="23">
+        <v>300.38</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1269,8 +1276,8 @@
       <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="5">
-        <v>225.27596778906121</v>
+      <c r="C5" s="23">
+        <v>225.28</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1280,8 +1287,8 @@
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="5">
-        <v>150.18786085409701</v>
+      <c r="C6" s="23">
+        <v>150.19</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1291,8 +1298,8 @@
       <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="5">
-        <v>193.5845238663006</v>
+      <c r="C7" s="23">
+        <v>193.58</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1302,8 +1309,8 @@
       <c r="B8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="5">
-        <v>165.89964249753839</v>
+      <c r="C8" s="23">
+        <v>165.9</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1313,8 +1320,8 @@
       <c r="B9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="5">
-        <v>129.06023157225661</v>
+      <c r="C9" s="23">
+        <v>129.06</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1324,8 +1331,8 @@
       <c r="B10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="5">
-        <v>110.59976166502561</v>
+      <c r="C10" s="23">
+        <v>110.6</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1335,8 +1342,8 @@
       <c r="B11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="5">
-        <v>75.088106934964188</v>
+      <c r="C11" s="23">
+        <v>75.09</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1346,8 +1353,8 @@
       <c r="B12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="5">
-        <v>64.524292294044017</v>
+      <c r="C12" s="23">
+        <v>64.52</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1357,8 +1364,8 @@
       <c r="B13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="5">
-        <v>55.299880832512805</v>
+      <c r="C13" s="23">
+        <v>55.3</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1368,8 +1375,8 @@
       <c r="B14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="5">
-        <v>129.06023157225661</v>
+      <c r="C14" s="23">
+        <v>129.06</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1379,8 +1386,8 @@
       <c r="B15" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="5">
-        <v>110.59976166502561</v>
+      <c r="C15" s="23">
+        <v>110.6</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1390,8 +1397,8 @@
       <c r="B16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="5">
-        <v>129.06023157225661</v>
+      <c r="C16" s="23">
+        <v>129.06</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1401,8 +1408,8 @@
       <c r="B17" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="5">
-        <v>110.59976166502561</v>
+      <c r="C17" s="23">
+        <v>110.6</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1412,8 +1419,8 @@
       <c r="B18" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="5">
-        <v>96.786438441065997</v>
+      <c r="C18" s="23">
+        <v>96.79</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -1423,8 +1430,8 @@
       <c r="B19" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="5">
-        <v>82.949821248769197</v>
+      <c r="C19" s="23">
+        <v>82.95</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1434,8 +1441,8 @@
       <c r="B20" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="5">
-        <v>64.524292294044017</v>
+      <c r="C20" s="23">
+        <v>64.52</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1445,8 +1452,8 @@
       <c r="B21" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="5">
-        <v>55.299880832512805</v>
+      <c r="C21" s="23">
+        <v>55.3</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1456,8 +1463,8 @@
       <c r="B22" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="5">
-        <v>57.571042745389803</v>
+      <c r="C22" s="23">
+        <v>57.57</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1467,8 +1474,8 @@
       <c r="B23" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="5">
-        <v>57.0003405211284</v>
+      <c r="C23" s="23">
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1478,8 +1485,8 @@
       <c r="B24" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="5">
-        <v>54.228358289001612</v>
+      <c r="C24" s="23">
+        <v>54.23</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1489,8 +1496,8 @@
       <c r="B25" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="5">
-        <v>92.11599778945741</v>
+      <c r="C25" s="23">
+        <v>92.12</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1500,8 +1507,8 @@
       <c r="B26" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="5">
-        <v>91.195886040138006</v>
+      <c r="C26" s="23">
+        <v>91.2</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1511,8 +1518,8 @@
       <c r="B27" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="5">
-        <v>86.770032056070008</v>
+      <c r="C27" s="23">
+        <v>86.77</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -1522,8 +1529,8 @@
       <c r="B28" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C28" s="5">
-        <v>115.14208549077961</v>
+      <c r="C28" s="23">
+        <v>115.14</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1533,8 +1540,8 @@
       <c r="B29" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C29" s="5">
-        <v>114.0006810422568</v>
+      <c r="C29" s="23">
+        <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1544,8 +1551,8 @@
       <c r="B30" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C30" s="5">
-        <v>108.4683635621718</v>
+      <c r="C30" s="23">
+        <v>108.47</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1555,8 +1562,8 @@
       <c r="B31" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C31" s="5">
-        <v>89.623543177377016</v>
+      <c r="C31" s="23">
+        <v>89.62</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1566,184 +1573,185 @@
       <c r="B32" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="5">
-        <v>84.906514589094016</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C32" s="23">
+        <v>84.91</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C33" s="5">
-        <v>74.494110742365592</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C33" s="23">
+        <v>74.489999999999995</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="5">
-        <v>66.376162776851402</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C34" s="23">
+        <v>66.38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="5">
-        <v>60.051850373301605</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C35" s="23">
+        <v>60.05</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C36" s="5">
-        <v>56.429638296867004</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C36" s="23">
+        <v>56.43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C37" s="5">
-        <v>52.714250347083599</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C37" s="23">
+        <v>52.71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C38" s="5">
-        <v>48.113691600486604</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C38" s="23">
+        <v>48.11</v>
+      </c>
+      <c r="D38" s="22"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="5">
-        <v>42.441610310378401</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C39" s="23">
+        <v>42.44</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="5">
-        <v>40.6829157009198</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C40" s="23">
+        <v>40.68</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C41" s="5">
-        <v>37.363525212868801</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C41" s="23">
+        <v>37.36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C42" s="5">
-        <v>31.260505508522407</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C42" s="23">
+        <v>31.26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C43" s="5">
-        <v>20.748287007469099</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C43" s="23">
+        <v>20.75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C44" s="5">
-        <v>24.816578577561074</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C44" s="23">
+        <v>24.82</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="5">
-        <v>30.91901593269905</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C45" s="23">
+        <v>30.92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C46" s="5">
-        <v>34.173649188772629</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C46" s="23">
+        <v>34.17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>45</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C47" s="5">
-        <v>98.172429557129405</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C47" s="23">
+        <v>98.17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>45</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C48" s="5">
-        <v>90.287421274987196</v>
+      <c r="C48" s="23">
+        <v>90.29</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1753,8 +1761,8 @@
       <c r="B49" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C49" s="5">
-        <v>84.347459349001227</v>
+      <c r="C49" s="23">
+        <v>84.35</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1764,8 +1772,8 @@
       <c r="B50" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C50" s="5">
-        <v>76.986565354446</v>
+      <c r="C50" s="23">
+        <v>76.989999999999995</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1775,8 +1783,8 @@
       <c r="B51" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C51" s="5">
-        <v>67.913564687106629</v>
+      <c r="C51" s="23">
+        <v>67.91</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1786,8 +1794,8 @@
       <c r="B52" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C52" s="5">
-        <v>65.094994518305413</v>
+      <c r="C52" s="23">
+        <v>65.09</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1797,8 +1805,8 @@
       <c r="B53" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C53" s="5">
-        <v>59.783969737423796</v>
+      <c r="C53" s="23">
+        <v>59.78</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1808,8 +1816,8 @@
       <c r="B54" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C54" s="5">
-        <v>50.012150019968402</v>
+      <c r="C54" s="23">
+        <v>50.01</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1819,8 +1827,8 @@
       <c r="B55" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C55" s="5">
-        <v>33.531667421399398</v>
+      <c r="C55" s="23">
+        <v>33.53</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1830,8 +1838,8 @@
       <c r="B56" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C56" s="5">
-        <v>40.112213476658397</v>
+      <c r="C56" s="23">
+        <v>40.11</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1841,8 +1849,8 @@
       <c r="B57" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C57" s="5">
-        <v>49.96556208329401</v>
+      <c r="C57" s="23">
+        <v>49.97</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1852,8 +1860,8 @@
       <c r="B58" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C58" s="5">
-        <v>55.2299989275012</v>
+      <c r="C58" s="23">
+        <v>55.23</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -1863,8 +1871,8 @@
       <c r="B59" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C59" s="5">
-        <v>120.10370074660321</v>
+      <c r="C59" s="23">
+        <v>120.1</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -1874,8 +1882,8 @@
       <c r="B60" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C60" s="5">
-        <v>112.85927659373401</v>
+      <c r="C60" s="23">
+        <v>112.86</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -1885,8 +1893,8 @@
       <c r="B61" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C61" s="5">
-        <v>105.4285006941672</v>
+      <c r="C61" s="23">
+        <v>105.43</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -1896,8 +1904,8 @@
       <c r="B62" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C62" s="5">
-        <v>96.227383200973208</v>
+      <c r="C62" s="23">
+        <v>96.23</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -1907,8 +1915,8 @@
       <c r="B63" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C63" s="5">
-        <v>84.894867604925409</v>
+      <c r="C63" s="23">
+        <v>84.89</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -1918,8 +1926,8 @@
       <c r="B64" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C64" s="5">
-        <v>81.377478386008221</v>
+      <c r="C64" s="23">
+        <v>81.38</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -1929,8 +1937,8 @@
       <c r="B65" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C65" s="5">
-        <v>74.727050425737602</v>
+      <c r="C65" s="23">
+        <v>74.73</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -1940,8 +1948,8 @@
       <c r="B66" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C66" s="5">
-        <v>62.521011017044813</v>
+      <c r="C66" s="23">
+        <v>62.52</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -1951,8 +1959,8 @@
       <c r="B67" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C67" s="5">
-        <v>41.917496022791411</v>
+      <c r="C67" s="23">
+        <v>41.92</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -1962,8 +1970,8 @@
       <c r="B68" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C68" s="5">
-        <v>50.1286198616544</v>
+      <c r="C68" s="23">
+        <v>50.13</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -1973,8 +1981,8 @@
       <c r="B69" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C69" s="5">
-        <v>62.462776096201807</v>
+      <c r="C69" s="23">
+        <v>62.46</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -1984,8 +1992,8 @@
       <c r="B70" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C70" s="5">
-        <v>69.031675167292207</v>
+      <c r="C70" s="23">
+        <v>69.03</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -1995,8 +2003,8 @@
       <c r="B71" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C71" s="5">
-        <v>32.56875300526039</v>
+      <c r="C71" s="23">
+        <v>32.57</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -2006,8 +2014,8 @@
       <c r="B72" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C72" s="5">
-        <v>30.724569532004267</v>
+      <c r="C72" s="23">
+        <v>30.72</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -2017,8 +2025,8 @@
       <c r="B73" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C73" s="5">
-        <v>29.601509083547018</v>
+      <c r="C73" s="23">
+        <v>29.6</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -2028,8 +2036,8 @@
       <c r="B74" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C74" s="5">
-        <v>28.773990858367988</v>
+      <c r="C74" s="23">
+        <v>28.77</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -2039,8 +2047,8 @@
       <c r="B75" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C75" s="5">
-        <v>27.970116011051214</v>
+      <c r="C75" s="23">
+        <v>27.97</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -2050,8 +2058,8 @@
       <c r="B76" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C76" s="5">
-        <v>87.79968369149509</v>
+      <c r="C76" s="23">
+        <v>87.8</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -2061,8 +2069,8 @@
       <c r="B77" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C77" s="5">
-        <v>46.21098203178326</v>
+      <c r="C77" s="23">
+        <v>46.21</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -2072,8 +2080,8 @@
       <c r="B78" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C78" s="5">
-        <v>87.79968369149509</v>
+      <c r="C78" s="23">
+        <v>87.8</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -2083,8 +2091,8 @@
       <c r="B79" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C79" s="5">
-        <v>66.54428699332513</v>
+      <c r="C79" s="23">
+        <v>66.540000000000006</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -2094,8 +2102,8 @@
       <c r="B80" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C80" s="5">
-        <v>55.455542775926133</v>
+      <c r="C80" s="23">
+        <v>55.46</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -2105,8 +2113,8 @@
       <c r="B81" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C81" s="5">
-        <v>35.985221106356676</v>
+      <c r="C81" s="23">
+        <v>35.99</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -2116,8 +2124,8 @@
       <c r="B82" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C82" s="5">
-        <v>33.514488119750716</v>
+      <c r="C82" s="23">
+        <v>33.51</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -2127,8 +2135,8 @@
       <c r="B83" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C83" s="5">
-        <v>26.811590495800573</v>
+      <c r="C83" s="23">
+        <v>26.81</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -2138,8 +2146,8 @@
       <c r="B84" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C84" s="5">
-        <v>69.712499626867711</v>
+      <c r="C84" s="23">
+        <v>69.709999999999994</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -2149,8 +2157,8 @@
       <c r="B85" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C85" s="5">
-        <v>34.21196776668733</v>
+      <c r="C85" s="23">
+        <v>34.21</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -2160,8 +2168,8 @@
       <c r="B86" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C86" s="5">
-        <v>59.250304922818543</v>
+      <c r="C86" s="23">
+        <v>59.25</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -2171,8 +2179,8 @@
       <c r="B87" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C87" s="5">
-        <v>47.038500256962287</v>
+      <c r="C87" s="23">
+        <v>47.04</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -2182,8 +2190,8 @@
       <c r="B88" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C88" s="5">
-        <v>76.840978052338485</v>
+      <c r="C88" s="23">
+        <v>76.84</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -2193,8 +2201,8 @@
       <c r="B89" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C89" s="5">
-        <v>23.643377862257996</v>
+      <c r="C89" s="23">
+        <v>23.64</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -2204,8 +2212,8 @@
       <c r="B90" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C90" s="5">
-        <v>72.112302479886907</v>
+      <c r="C90" s="23">
+        <v>72.11</v>
       </c>
     </row>
   </sheetData>
@@ -2223,7 +2231,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>216</v>
       </c>
     </row>
@@ -2231,711 +2239,711 @@
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="22">
+      <c r="B2" s="20">
         <v>2025</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="B3" s="10">
+      <c r="A3" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="21">
         <v>209391.81077992453</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="B4" s="10">
+      <c r="A4" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="21">
         <v>205285.08416207618</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="B5" s="10">
+      <c r="A5" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" s="21">
         <v>180016.95200829845</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="B6" s="10">
+      <c r="A6" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" s="21">
         <v>176486.75110679585</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="B7" s="10">
+      <c r="A7" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B7" s="21">
         <v>171253.76111984384</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="B8" s="10">
+        <v>133</v>
+      </c>
+      <c r="B8" s="21">
         <v>166012.61824397382</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="B9" s="10">
+      <c r="A9" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="21">
         <v>157329.79154628253</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="B10" s="10">
+      <c r="A10" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" s="21">
         <v>154244.50544002038</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="B11" s="10">
+      <c r="A11" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B11" s="21">
         <v>150314.81298153472</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="B12" s="10">
+      <c r="A12" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12" s="21">
         <v>146393.27341196712</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="B13" s="10">
+      <c r="A13" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" s="21">
         <v>142463.58095348146</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="B14" s="10">
+      <c r="A14" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14" s="21">
         <v>138536.21789182955</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="B15" s="10">
+        <v>140</v>
+      </c>
+      <c r="B15" s="21">
         <v>133236.84009511655</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="B16" s="10">
+        <v>141</v>
+      </c>
+      <c r="B16" s="21">
         <v>130623.25684768271</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="B17" s="10">
+        <v>142</v>
+      </c>
+      <c r="B17" s="21">
         <v>126694.72908761395</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B18" s="21">
+        <v>122724.27218453819</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="B19" s="21">
+        <v>118737.50950362642</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="B20" s="21">
+        <v>114765.88790213382</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="B21" s="21">
+        <v>107586.68686060878</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="B22" s="21">
+        <v>105477.41802767532</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="B23" s="21">
+        <v>102029.91071376971</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="B24" s="21">
+        <v>98577.744606196662</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="B25" s="21">
+        <v>95131.401990707935</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B26" s="21">
+        <v>91686.224073636069</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="B27" s="21">
+        <v>87438.568947347623</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="B28" s="21">
+        <v>83197.902011560393</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B29" s="21">
+        <v>139557.65840341579</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="B30" s="21">
+        <v>137494.97750715673</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="B31" s="21">
+        <v>137276.01420478706</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B32" s="21">
+        <v>135247.10956261691</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="B33" s="21">
+        <v>133500.06193732691</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B34" s="21">
+        <v>131870.6488521398</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="B35" s="21">
+        <v>130242.40046536949</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="B36" s="21">
+        <v>129941.90827381963</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B37" s="21">
+        <v>128021.32058441748</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="B38" s="21">
+        <v>124585.46025468048</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="B39" s="21">
+        <v>121144.94113127605</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B40" s="21">
+        <v>117718.39838887392</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="B18" s="10">
-        <v>122724.27218453819</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+      <c r="B41" s="21">
+        <v>114282.53805913692</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="B19" s="10">
-        <v>118737.50950362642</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+      <c r="B42" s="21">
+        <v>111915.87087607739</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="B20" s="10">
-        <v>114765.88790213382</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="B43" s="21">
+        <v>110261.99912413621</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="B21" s="10">
-        <v>107586.68686060878</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="B44" s="21">
+        <v>107443.428955335</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="B22" s="10">
-        <v>105477.41802767532</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
+      <c r="B45" s="21">
+        <v>104635.34107228555</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="B23" s="10">
-        <v>102029.91071376971</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
+      <c r="B46" s="21">
+        <v>101821.42969715179</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="B24" s="10">
-        <v>98577.744606196662</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
+      <c r="B47" s="21">
+        <v>99890.359721997898</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B25" s="10">
-        <v>95131.401990707935</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
+      <c r="B48" s="21">
+        <v>98414.686827836296</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B26" s="10">
-        <v>91686.224073636069</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
+      <c r="B49" s="21">
+        <v>96320.559074322009</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="B27" s="10">
-        <v>87438.568947347623</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
+      <c r="B50" s="21">
+        <v>94220.607828723412</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="B28" s="10">
-        <v>83197.902011560393</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
+      <c r="B51" s="21">
+        <v>92120.65658312483</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="B29" s="10">
-        <v>139557.65840341579</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="15" t="s">
+      <c r="B52" s="21">
+        <v>90311.879941741267</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="B30" s="10">
-        <v>137494.97750715673</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="15" t="s">
+      <c r="B53" s="21">
+        <v>89418.556256009644</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="B31" s="10">
-        <v>137276.01420478706</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="15" t="s">
+      <c r="B54" s="21">
+        <v>86563.880436285792</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="B32" s="10">
-        <v>135247.10956261691</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="15" t="s">
+      <c r="B55" s="21">
+        <v>83719.686902313653</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="B33" s="10">
-        <v>133500.06193732691</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="16" t="s">
+      <c r="B56" s="21">
+        <v>80868.505177840387</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="B34" s="10">
-        <v>131870.6488521398</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="s">
+      <c r="B57" s="21">
+        <v>78195.522311146677</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="B35" s="10">
-        <v>130242.40046536949</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
+      <c r="B58" s="21">
+        <v>77420.997863934783</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="B36" s="10">
-        <v>129941.90827381963</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="16" t="s">
+      <c r="B59" s="21">
+        <v>75621.538809886071</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="B37" s="10">
-        <v>128021.32058441748</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="17" t="s">
+      <c r="B60" s="21">
+        <v>73813.926866919341</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="B38" s="10">
-        <v>124585.46025468048</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="17" t="s">
+      <c r="B61" s="21">
+        <v>72133.267051390372</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="B39" s="10">
-        <v>121144.94113127605</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="17" t="s">
+      <c r="B62" s="21">
+        <v>71419.306921855197</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="B40" s="10">
-        <v>117718.39838887392</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="17" t="s">
+      <c r="B63" s="21">
+        <v>69310.038088921734</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="B41" s="10">
-        <v>114282.53805913692</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="17" t="s">
+      <c r="B64" s="21">
+        <v>67220.569129074909</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="B42" s="10">
-        <v>111915.87087607739</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="18" t="s">
+      <c r="B65" s="21">
+        <v>65113.629692975162</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="B43" s="10">
-        <v>110261.99912413621</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="18" t="s">
+      <c r="B66" s="21">
+        <v>63039.301812547506</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="B44" s="10">
-        <v>107443.428955335</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="14" t="s">
+      <c r="B67" s="21">
+        <v>62415.023461110533</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="B45" s="10">
-        <v>104635.34107228555</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="14" t="s">
+      <c r="B68" s="21">
+        <v>60008.756531877778</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="B46" s="10">
-        <v>101821.42969715179</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="14" t="s">
+      <c r="B69" s="21">
+        <v>59414.760339279186</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="B47" s="10">
-        <v>99890.359721997898</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="19" t="s">
+      <c r="B70" s="21">
+        <v>57317.138490514313</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="B71" s="21">
+        <v>138059.85623933381</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="B72" s="21">
+        <v>136692.50029794016</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="B73" s="21">
+        <v>134667.08975102063</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="B74" s="21">
+        <v>129039.26700075311</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="B75" s="21">
+        <v>88313.828389006012</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="B76" s="21">
+        <v>87439.162715168</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="B77" s="21">
+        <v>83197.148383173</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="B78" s="21">
+        <v>119423.51687115696</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="B79" s="21">
+        <v>118241.34797804405</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="B80" s="21">
+        <v>114642.42986994666</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="B81" s="21">
+        <v>110817.56026897841</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="B48" s="10">
-        <v>98414.686827836296</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="19" t="s">
+      <c r="B82" s="21">
+        <v>104653.97624695531</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="B49" s="10">
-        <v>96320.559074322009</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="19" t="s">
+      <c r="B83" s="21">
+        <v>100791.83629664755</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="B50" s="10">
-        <v>94220.607828723412</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="19" t="s">
+      <c r="B84" s="21">
+        <v>97898.725429167302</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="B51" s="10">
-        <v>92120.65658312483</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="19" t="s">
+      <c r="B85" s="21">
+        <v>96929.696346339784</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="B52" s="10">
-        <v>90311.879941741267</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="19" t="s">
+      <c r="B86" s="21">
+        <v>94245.066495477498</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="B53" s="10">
-        <v>89418.556256009644</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="19" t="s">
+      <c r="B87" s="21">
+        <v>91200.544833805441</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="B54" s="10">
-        <v>86563.880436285792</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="19" t="s">
+      <c r="B88" s="21">
+        <v>87932.401076096285</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="B55" s="10">
-        <v>83719.686902313653</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="19" t="s">
+      <c r="B89" s="21">
+        <v>82871.786454839588</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="B56" s="10">
-        <v>80868.505177840387</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="B57" s="10">
-        <v>78195.522311146677</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="B58" s="10">
-        <v>77420.997863934783</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="B59" s="10">
-        <v>75621.538809886071</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="B60" s="10">
-        <v>73813.926866919341</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="B61" s="10">
-        <v>72133.267051390372</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="B62" s="10">
-        <v>71419.306921855197</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="17" t="s">
-        <v>198</v>
-      </c>
-      <c r="B63" s="10">
-        <v>69310.038088921734</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="B64" s="10">
-        <v>67220.569129074909</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="B65" s="10">
-        <v>65113.629692975162</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="B66" s="10">
-        <v>63039.301812547506</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="B67" s="10">
-        <v>62415.023461110533</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="B68" s="10">
-        <v>60008.756531877778</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="B69" s="10">
-        <v>59414.760339279186</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="B70" s="10">
-        <v>57317.138490514313</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="B71" s="10">
-        <v>138059.85623933381</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="B72" s="10">
-        <v>136692.50029794016</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="B73" s="10">
-        <v>134667.08975102063</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="B74" s="10">
-        <v>129039.26700075311</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="B75" s="10">
-        <v>88313.828389006012</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="B76" s="10">
-        <v>87439.162715168</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="B77" s="10">
-        <v>83197.148383173</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="B78" s="10">
-        <v>119423.51687115696</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="B79" s="10">
-        <v>118241.34797804405</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="B80" s="10">
-        <v>114642.42986994666</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="B81" s="10">
-        <v>110817.56026897841</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="B82" s="10">
-        <v>104653.97624695531</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="B83" s="10">
-        <v>100791.83629664755</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="B84" s="10">
-        <v>97898.725429167302</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="B85" s="10">
-        <v>96929.696346339784</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="B86" s="10">
-        <v>94245.066495477498</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="B87" s="10">
-        <v>91200.544833805441</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="B88" s="10">
-        <v>87932.401076096285</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="B89" s="10">
-        <v>82871.786454839588</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="B90" s="10">
+      <c r="B90" s="21">
         <v>77821.65411933462</v>
       </c>
     </row>
